--- a/output/yearly_surface_area_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_18_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622986865</v>
+        <v>10.84497619922416</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907158528577</v>
+        <v>37.78907147850576</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.419067400993145</v>
+        <v>5.277875658030853</v>
       </c>
       <c r="C2" t="n">
-        <v>6.616979526623502</v>
+        <v>7.435757111965342</v>
       </c>
       <c r="D2" t="n">
-        <v>17.67833091037232</v>
+        <v>32.15616430490002</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.90002596508285</v>
+        <v>15.20236320026186</v>
       </c>
       <c r="C3" t="n">
-        <v>28.34305622160542</v>
+        <v>31.33247798103696</v>
       </c>
       <c r="D3" t="n">
-        <v>65.96362824834318</v>
+        <v>69.22303062644259</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.90902592533709</v>
+        <v>28.74164578952962</v>
       </c>
       <c r="C4" t="n">
-        <v>68.36989187145213</v>
+        <v>67.96148482648545</v>
       </c>
       <c r="D4" t="n">
-        <v>94.07401026404212</v>
+        <v>81.75798531426587</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.62734644967627</v>
+        <v>35.80924751240241</v>
       </c>
       <c r="C5" t="n">
-        <v>110.6675099612217</v>
+        <v>107.3295677667826</v>
       </c>
       <c r="D5" t="n">
-        <v>73.70470889632931</v>
+        <v>61.01561981893928</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.77242412572655</v>
+        <v>34.45541742824607</v>
       </c>
       <c r="C6" t="n">
-        <v>128.8052987971816</v>
+        <v>142.7323717296268</v>
       </c>
       <c r="D6" t="n">
-        <v>50.39507315439728</v>
+        <v>44.07556318216056</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.69808903764427</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="C7" t="n">
-        <v>118.815034158766</v>
+        <v>150.8543704868606</v>
       </c>
       <c r="D7" t="n">
-        <v>39.70482240285375</v>
+        <v>38.32743037379547</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.27385085622263</v>
+        <v>13.10142311317368</v>
       </c>
       <c r="C8" t="n">
-        <v>86.20235717139117</v>
+        <v>110.0686438616311</v>
       </c>
       <c r="D8" t="n">
         <v>35.79943003535994</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.098436812331936</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59374604355361</v>
+        <v>55.35780779936488</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.658494574694808</v>
+        <v>7.663875262956981</v>
       </c>
       <c r="C21" t="n">
-        <v>92.85924671817455</v>
+        <v>92.92448756335338</v>
       </c>
       <c r="D21" t="n">
-        <v>7.658494574694808</v>
+        <v>7.663875262956981</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.443611093599316</v>
+        <v>5.494841900669398</v>
       </c>
       <c r="C2" t="n">
-        <v>14.01935721664445</v>
+        <v>9.205848222722341</v>
       </c>
       <c r="D2" t="n">
-        <v>31.72812230584842</v>
+        <v>25.50580535633214</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.16786316189298</v>
+        <v>16.42463909204914</v>
       </c>
       <c r="C3" t="n">
-        <v>26.84589097262903</v>
+        <v>29.91385254840031</v>
       </c>
       <c r="D3" t="n">
-        <v>64.57936398535519</v>
+        <v>77.02301613668351</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.81143199198916</v>
+        <v>28.39705234533899</v>
       </c>
       <c r="C4" t="n">
-        <v>69.44196036448963</v>
+        <v>72.88789480639595</v>
       </c>
       <c r="D4" t="n">
-        <v>103.8502539029318</v>
+        <v>95.29923139894213</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.92249265575607</v>
+        <v>38.8772090881737</v>
       </c>
       <c r="C5" t="n">
-        <v>116.6807146497334</v>
+        <v>114.594500778209</v>
       </c>
       <c r="D5" t="n">
-        <v>87.20373982972295</v>
+        <v>73.33655350723674</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.78879504152925</v>
+        <v>40.65417243286043</v>
       </c>
       <c r="C6" t="n">
-        <v>150.8229545603247</v>
+        <v>156.0556698239603</v>
       </c>
       <c r="D6" t="n">
-        <v>60.53849043467533</v>
+        <v>52.04539104523617</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.11835917051991</v>
+        <v>32.09922293805371</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9978855781299</v>
+        <v>175.8270868397867</v>
       </c>
       <c r="D7" t="n">
-        <v>44.0765449298648</v>
+        <v>41.56130731158447</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.61870634232051</v>
+        <v>18.94282195344221</v>
       </c>
       <c r="C8" t="n">
-        <v>119.5817791157827</v>
+        <v>152.2101640664255</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.20312396378785</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>91.30155474724909</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>42.13661146627311</v>
+        <v>47.54604131667303</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>29.94134148411922</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.833716193710189</v>
+        <v>7.838530658840989</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8590959940187</v>
+        <v>100.9210822325777</v>
       </c>
       <c r="D21" t="n">
-        <v>8.812930717923962</v>
+        <v>8.818346991196112</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.146542449840032</v>
+        <v>5.848271074198249</v>
       </c>
       <c r="C2" t="n">
-        <v>9.6034560429423</v>
+        <v>15.38889526406875</v>
       </c>
       <c r="D2" t="n">
-        <v>37.00501621617502</v>
+        <v>22.41820882647592</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.91399141712056</v>
+        <v>16.94496537529995</v>
       </c>
       <c r="C3" t="n">
-        <v>39.10301106015046</v>
+        <v>32.27986451563513</v>
       </c>
       <c r="D3" t="n">
-        <v>71.7313960107932</v>
+        <v>78.15202599656735</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3219407981975</v>
+        <v>28.94584931201296</v>
       </c>
       <c r="C4" t="n">
-        <v>67.47650146058751</v>
+        <v>72.73474216453344</v>
       </c>
       <c r="D4" t="n">
-        <v>108.9170538045496</v>
+        <v>106.5942387363017</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.76326960121884</v>
+        <v>40.07985002587604</v>
       </c>
       <c r="C5" t="n">
-        <v>120.0922879219911</v>
+        <v>121.663084248786</v>
       </c>
       <c r="D5" t="n">
-        <v>100.7518581483289</v>
+        <v>86.93375921105508</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.30956329313658</v>
+        <v>45.76613272887356</v>
       </c>
       <c r="C6" t="n">
-        <v>165.8368222013712</v>
+        <v>167.5273917480843</v>
       </c>
       <c r="D6" t="n">
-        <v>70.23913950033806</v>
+        <v>60.01521890831177</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.4007837141735</v>
+        <v>38.5669768136317</v>
       </c>
       <c r="C7" t="n">
-        <v>177.0248190389678</v>
+        <v>196.0687610059475</v>
       </c>
       <c r="D7" t="n">
-        <v>49.88554609589318</v>
+        <v>46.05280305851362</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.04701038327938</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="C8" t="n">
-        <v>151.9598184018425</v>
+        <v>186.0902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>39.72151211382594</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.63906100220244</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>105.1687410697353</v>
+        <v>132.570301242968</v>
       </c>
       <c r="D9" t="n">
         <v>36.60937189136354</v>
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>60.07314202286233</v>
+        <v>71.60376880924112</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.27088991757665</v>
+        <v>41.5809422656694</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1590,7 +1590,7 @@
         <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.992217265586326</v>
+        <v>7.997667998287402</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8949330854154</v>
+        <v>108.9682264766658</v>
       </c>
       <c r="D21" t="n">
-        <v>9.990271581982906</v>
+        <v>9.997084997859252</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.58105577219387</v>
+        <v>5.434955290710342</v>
       </c>
       <c r="C2" t="n">
-        <v>6.607162049581034</v>
+        <v>10.5871672425976</v>
       </c>
       <c r="D2" t="n">
-        <v>30.29182541453534</v>
+        <v>18.6846223072253</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.13550654538184</v>
+        <v>20.16509784522949</v>
       </c>
       <c r="C3" t="n">
-        <v>53.87831400906496</v>
+        <v>51.4190360099267</v>
       </c>
       <c r="D3" t="n">
-        <v>78.28456193664067</v>
+        <v>83.86579763528378</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.78894960578271</v>
+        <v>19.24618199405447</v>
       </c>
       <c r="C4" t="n">
-        <v>96.21814725011714</v>
+        <v>99.82999705404117</v>
       </c>
       <c r="D4" t="n">
-        <v>107.3089510649934</v>
+        <v>100.8254892261474</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.09748042682348</v>
+        <v>25.77087723647878</v>
       </c>
       <c r="C5" t="n">
-        <v>99.08288705110937</v>
+        <v>100.0891784479623</v>
       </c>
       <c r="D5" t="n">
-        <v>69.04140730115695</v>
+        <v>59.22393025868885</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.52333794628834</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="C6" t="n">
-        <v>116.5687954114493</v>
+        <v>129.1273120441745</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.51736534460484</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>106.8377121669549</v>
+        <v>130.8522427605361</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>77.52370746584938</v>
+        <v>97.71825774220626</v>
       </c>
       <c r="D8" t="n">
         <v>26.95388322009618</v>
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>54.58124536530566</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1887,7 +1887,7 @@
         <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.726133448244146</v>
+        <v>3.281982575297087</v>
       </c>
       <c r="C2" t="n">
-        <v>3.222095965338032</v>
+        <v>5.089380098815464</v>
       </c>
       <c r="D2" t="n">
-        <v>22.10699480422968</v>
+        <v>13.07000718663779</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.61656292046278</v>
+        <v>19.98838325846506</v>
       </c>
       <c r="C3" t="n">
-        <v>40.88979188187965</v>
+        <v>47.33496556025997</v>
       </c>
       <c r="D3" t="n">
-        <v>84.4744812119168</v>
+        <v>81.13653901747765</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.17780381212246</v>
+        <v>27.19735665074939</v>
       </c>
       <c r="C4" t="n">
-        <v>116.7788894201581</v>
+        <v>115.8982617294487</v>
       </c>
       <c r="D4" t="n">
-        <v>118.9230264062331</v>
+        <v>115.6047191658789</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.72994693253668</v>
+        <v>28.27433388230815</v>
       </c>
       <c r="C5" t="n">
-        <v>136.4138435050943</v>
+        <v>139.8499604699582</v>
       </c>
       <c r="D5" t="n">
-        <v>86.05018627723294</v>
+        <v>75.91364123088462</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.64158963915446</v>
+        <v>28.41766904712818</v>
       </c>
       <c r="C6" t="n">
-        <v>137.9826763364807</v>
+        <v>147.522318778647</v>
       </c>
       <c r="D6" t="n">
-        <v>40.33215918586747</v>
+        <v>36.58875518957439</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.02020009562846</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>133.7866866485298</v>
+        <v>158.5198565616197</v>
       </c>
       <c r="D7" t="n">
-        <v>31.02126395879071</v>
+        <v>30.30262463928205</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>99.72102305886976</v>
+        <v>124.6721409623024</v>
       </c>
       <c r="D8" t="n">
         <v>27.70492021384499</v>
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>51.14218315732908</v>
+        <v>60.23905738488002</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2156,7 +2156,7 @@
         <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2184,7 +2184,7 @@
         <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.284167054883833</v>
+        <v>2.809761929554371</v>
       </c>
       <c r="C2" t="n">
-        <v>6.546293691917731</v>
+        <v>4.899902791895831</v>
       </c>
       <c r="D2" t="n">
-        <v>24.95700838965817</v>
+        <v>12.23650338573225</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.81934272688536</v>
+        <v>15.56070111231194</v>
       </c>
       <c r="C3" t="n">
-        <v>26.19793748782614</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D3" t="n">
-        <v>82.33917995517999</v>
+        <v>73.5329030480861</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.72057142385071</v>
+        <v>32.51941095547134</v>
       </c>
       <c r="C4" t="n">
-        <v>109.3254608495163</v>
+        <v>116.9192793418654</v>
       </c>
       <c r="D4" t="n">
-        <v>131.7367974420625</v>
+        <v>127.6399642722406</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.38757902566179</v>
+        <v>33.89483948912113</v>
       </c>
       <c r="C5" t="n">
-        <v>174.1865864259904</v>
+        <v>175.1928778228433</v>
       </c>
       <c r="D5" t="n">
-        <v>105.3415286656828</v>
+        <v>96.08855655315659</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.80009298789471</v>
+        <v>32.8453511932813</v>
       </c>
       <c r="C6" t="n">
-        <v>175.8594845140269</v>
+        <v>183.6683057536061</v>
       </c>
       <c r="D6" t="n">
-        <v>54.29948377418685</v>
+        <v>48.74475526355839</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.96137734883166</v>
+        <v>22.87668500435917</v>
       </c>
       <c r="C7" t="n">
-        <v>165.1672702670749</v>
+        <v>185.6484908730718</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>134.6025189907589</v>
+        <v>163.5591675275186</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.545311944213482</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>81.09530561389926</v>
+        <v>98.95624159726147</v>
       </c>
       <c r="D9" t="n">
         <v>29.17656002251095</v>
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>44.4142661401257</v>
+        <v>49.25428232206248</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2495,7 +2495,7 @@
         <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.753221473335556</v>
+        <v>1.690569546713007</v>
       </c>
       <c r="C2" t="n">
-        <v>3.114103717870883</v>
+        <v>2.350304003966864</v>
       </c>
       <c r="D2" t="n">
-        <v>17.4054050485917</v>
+        <v>8.536296288426016</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.2085157283946</v>
+        <v>14.67712817848982</v>
       </c>
       <c r="C3" t="n">
-        <v>27.58220175081414</v>
+        <v>29.32480392585222</v>
       </c>
       <c r="D3" t="n">
-        <v>84.90645020178539</v>
+        <v>70.59747741238813</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.05989627662161</v>
+        <v>35.5952265128766</v>
       </c>
       <c r="C4" t="n">
-        <v>104.4883899106923</v>
+        <v>115.9237871697591</v>
       </c>
       <c r="D4" t="n">
-        <v>141.6917191631252</v>
+        <v>135.8463933320397</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.22835597112457</v>
+        <v>35.26928627506667</v>
       </c>
       <c r="C5" t="n">
-        <v>209.2104357749953</v>
+        <v>211.6893487282185</v>
       </c>
       <c r="D5" t="n">
-        <v>110.9620342724958</v>
+        <v>101.5863436969387</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.99127174831558</v>
+        <v>27.25037102677872</v>
       </c>
       <c r="C6" t="n">
-        <v>208.8658423308047</v>
+        <v>223.3161867896135</v>
       </c>
       <c r="D6" t="n">
-        <v>53.05168244208915</v>
+        <v>47.97997380195012</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>174.6892412505647</v>
+        <v>202.4167416616073</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>99.30378028456487</v>
+        <v>121.0004045484194</v>
       </c>
       <c r="D8" t="n">
-        <v>31.12631096314512</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2792,7 +2792,7 @@
         <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.659374604355362</v>
+        <v>2.549598787928967</v>
       </c>
       <c r="C2" t="n">
-        <v>4.027129082820416</v>
+        <v>7.089200172366218</v>
       </c>
       <c r="D2" t="n">
-        <v>21.31766965001524</v>
+        <v>9.556332153138452</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.26050729899067</v>
+        <v>10.33289458719768</v>
       </c>
       <c r="C3" t="n">
-        <v>19.87057353395544</v>
+        <v>19.24225500323749</v>
       </c>
       <c r="D3" t="n">
-        <v>80.30205346886785</v>
+        <v>62.73367830137119</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.69879304790803</v>
+        <v>32.39178375391926</v>
       </c>
       <c r="C4" t="n">
-        <v>87.20766682053993</v>
+        <v>95.22265507801089</v>
       </c>
       <c r="D4" t="n">
-        <v>149.5280293384232</v>
+        <v>139.0370733708418</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.88031856220246</v>
+        <v>42.87783098297945</v>
       </c>
       <c r="C5" t="n">
-        <v>203.1972310864836</v>
+        <v>214.2664364518664</v>
       </c>
       <c r="D5" t="n">
-        <v>130.8424252834937</v>
+        <v>121.4667347079366</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.93972214607601</v>
+        <v>35.17994723398021</v>
       </c>
       <c r="C6" t="n">
-        <v>264.4131274370893</v>
+        <v>274.5967963732414</v>
       </c>
       <c r="D6" t="n">
-        <v>69.6756163181004</v>
+        <v>63.27560303411543</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.24167416616073</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="C7" t="n">
-        <v>231.3419742718311</v>
+        <v>257.153103164184</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>152.0432669567035</v>
+        <v>180.0819813899924</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>65.56405693271472</v>
+        <v>77.32343093418301</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3117,7 +3117,7 @@
         <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.105267988532661</v>
+        <v>1.670934592628071</v>
       </c>
       <c r="C2" t="n">
-        <v>2.519164609097316</v>
+        <v>4.015348110369454</v>
       </c>
       <c r="D2" t="n">
-        <v>16.12127905143687</v>
+        <v>7.967864367667113</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.38184310368978</v>
+        <v>9.714393533522189</v>
       </c>
       <c r="C3" t="n">
-        <v>18.33904711533042</v>
+        <v>23.37541283811656</v>
       </c>
       <c r="D3" t="n">
-        <v>79.85535826343556</v>
+        <v>58.12437282993241</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.7551125199486</v>
+        <v>28.15456066239003</v>
       </c>
       <c r="C4" t="n">
-        <v>73.90891241881263</v>
+        <v>77.27827053978768</v>
       </c>
       <c r="D4" t="n">
-        <v>153.8035405904181</v>
+        <v>139.1391751320834</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.69717370986481</v>
+        <v>46.53484118129882</v>
       </c>
       <c r="C5" t="n">
-        <v>192.5452684954057</v>
+        <v>206.9524160552277</v>
       </c>
       <c r="D5" t="n">
-        <v>145.9122525436822</v>
+        <v>134.3276296335698</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.11080828852221</v>
+        <v>41.13719230334986</v>
       </c>
       <c r="C6" t="n">
-        <v>296.0911806100211</v>
+        <v>309.0924654573616</v>
       </c>
       <c r="D6" t="n">
-        <v>81.30834486572085</v>
+        <v>76.11588125795947</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="C7" t="n">
-        <v>285.180036625022</v>
+        <v>310.2725261978662</v>
       </c>
       <c r="D7" t="n">
-        <v>44.73529763941441</v>
+        <v>42.39971985101125</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>193.2668530580271</v>
+        <v>224.893855350338</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>73.77343123562655</v>
+        <v>87.08593010521329</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.333434366545421</v>
+        <v>2.796999209399163</v>
       </c>
       <c r="C2" t="n">
-        <v>7.42692138262712</v>
+        <v>8.642325040484671</v>
       </c>
       <c r="D2" t="n">
-        <v>13.98303255158732</v>
+        <v>7.793113276311181</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.09298829446296</v>
+        <v>7.785259294677207</v>
       </c>
       <c r="C3" t="n">
-        <v>14.36787765165207</v>
+        <v>19.85584731839174</v>
       </c>
       <c r="D3" t="n">
-        <v>74.83371875621312</v>
+        <v>52.20934291184538</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.87975342065894</v>
+        <v>23.59826956698058</v>
       </c>
       <c r="C4" t="n">
-        <v>61.54183658841556</v>
+        <v>68.85487523735006</v>
       </c>
       <c r="D4" t="n">
-        <v>156.8665934276681</v>
+        <v>136.6249192615074</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.94261063592651</v>
+        <v>45.3076565509903</v>
       </c>
       <c r="C5" t="n">
-        <v>168.6887992822082</v>
+        <v>179.6843735697725</v>
       </c>
       <c r="D5" t="n">
-        <v>161.595672119025</v>
+        <v>148.1457285708437</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>67.22026530977911</v>
+        <v>48.50324532831367</v>
       </c>
       <c r="C6" t="n">
-        <v>301.0018826266636</v>
+        <v>317.8673264379196</v>
       </c>
       <c r="D6" t="n">
-        <v>99.94486153543805</v>
+        <v>93.10208003683779</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.53650157707104</v>
+        <v>25.21226279276233</v>
       </c>
       <c r="C7" t="n">
-        <v>341.3536767666159</v>
+        <v>364.3501349908932</v>
       </c>
       <c r="D7" t="n">
-        <v>53.23919625360028</v>
+        <v>50.2448657556475</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>265.0326102384689</v>
+        <v>295.9085755370311</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>131.9046762994887</v>
+        <v>156.4218617176442</v>
       </c>
       <c r="D9" t="n">
         <v>32.8374972116473</v>
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>56.37195317785186</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
         <v>24.6997904911455</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.806857744170636</v>
+        <v>4.597524498987813</v>
       </c>
       <c r="C2" t="n">
-        <v>9.880308895539899</v>
+        <v>12.63901994447344</v>
       </c>
       <c r="D2" t="n">
-        <v>10.15323475732051</v>
+        <v>10.43205110532661</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.134720419660066</v>
+        <v>2.019455027635689</v>
       </c>
       <c r="C2" t="n">
-        <v>4.336379609658161</v>
+        <v>4.977460860531329</v>
       </c>
       <c r="D2" t="n">
-        <v>10.4025986741992</v>
+        <v>5.797220193577415</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.45685683984004</v>
+        <v>10.68632376072653</v>
       </c>
       <c r="C3" t="n">
-        <v>20.57252314249191</v>
+        <v>26.83116475706533</v>
       </c>
       <c r="D3" t="n">
-        <v>79.80627087822322</v>
+        <v>55.8319919405161</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.57865997509143</v>
+        <v>33.7956829709922</v>
       </c>
       <c r="C4" t="n">
-        <v>90.09204157561705</v>
+        <v>100.6468111439745</v>
       </c>
       <c r="D4" t="n">
-        <v>160.2104261083327</v>
+        <v>140.4664980282251</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.04901493641689</v>
+        <v>28.1516154192773</v>
       </c>
       <c r="C5" t="n">
-        <v>254.1744806294992</v>
+        <v>269.416113737931</v>
       </c>
       <c r="D5" t="n">
-        <v>146.2067768549562</v>
+        <v>134.4748917892069</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.81010608691964</v>
+        <v>15.65789413503238</v>
       </c>
       <c r="C6" t="n">
-        <v>280.876054689604</v>
+        <v>299.1503064564541</v>
       </c>
       <c r="D6" t="n">
-        <v>79.45676869551137</v>
+        <v>74.38506005537235</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>186.3671301925805</v>
+        <v>208.1059696077176</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>97.2175664130404</v>
+        <v>115.2424542630118</v>
       </c>
       <c r="D8" t="n">
         <v>24.20008090968387</v>
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>43.04374634499714</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4316,7 +4316,7 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
         <v>19.3600647277471</v>
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.231553589482005</v>
+        <v>5.855143308127976</v>
       </c>
       <c r="C2" t="n">
-        <v>6.515859513086081</v>
+        <v>10.00597260168349</v>
       </c>
       <c r="D2" t="n">
-        <v>27.02162381168921</v>
+        <v>10.64116336633118</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.57680998620739</v>
+        <v>9.773298395776997</v>
       </c>
       <c r="C3" t="n">
-        <v>24.89712177969911</v>
+        <v>31.84789552576653</v>
       </c>
       <c r="D3" t="n">
-        <v>11.66316272645211</v>
+        <v>11.89878217547134</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39722328400441</v>
+        <v>13.3972527197167</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13840425155249</v>
+        <v>70.1385583561639</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576143915765224</v>
+        <v>1.5761473787902</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.867505117655686</v>
+        <v>4.50622196249286</v>
       </c>
       <c r="C2" t="n">
-        <v>6.225262192629025</v>
+        <v>5.104106314379167</v>
       </c>
       <c r="D2" t="n">
-        <v>22.49576689511141</v>
+        <v>17.49965282819939</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.67208057124834</v>
+        <v>16.02212253330795</v>
       </c>
       <c r="C3" t="n">
-        <v>25.21618978357932</v>
+        <v>36.33448253417446</v>
       </c>
       <c r="D3" t="n">
-        <v>31.53864499892878</v>
+        <v>17.96107424919539</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.15684295296801</v>
+        <v>11.47368541953247</v>
       </c>
       <c r="C4" t="n">
-        <v>38.49236398810894</v>
+        <v>49.07265899677682</v>
       </c>
       <c r="D4" t="n">
-        <v>21.18611545764617</v>
+        <v>21.30097993904305</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
         <v>5.522330836388309</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>39.82655911818034</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43552752324093</v>
+        <v>15.438185717876</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1139956559757</v>
+        <v>86.12882558393979</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249584741734932</v>
+        <v>3.250144361658105</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.679410469067798</v>
+        <v>3.926009069282995</v>
       </c>
       <c r="C2" t="n">
-        <v>3.908337610606552</v>
+        <v>5.479133937401449</v>
       </c>
       <c r="D2" t="n">
-        <v>24.82839944040184</v>
+        <v>22.45060650071606</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.94282195344221</v>
+        <v>15.79141182280995</v>
       </c>
       <c r="C3" t="n">
-        <v>24.6075062069463</v>
+        <v>26.48755306057895</v>
       </c>
       <c r="D3" t="n">
-        <v>42.21515128261285</v>
+        <v>27.7932775072272</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68983414538279</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="C4" t="n">
-        <v>52.76108512163209</v>
+        <v>72.84960664593032</v>
       </c>
       <c r="D4" t="n">
-        <v>32.21310567174634</v>
+        <v>25.52544031041707</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.32155558310323</v>
+        <v>10.35743827980385</v>
       </c>
       <c r="C5" t="n">
-        <v>42.16606389740051</v>
+        <v>54.02066742618075</v>
       </c>
       <c r="D5" t="n">
-        <v>30.55689729468198</v>
+        <v>30.31146036862028</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.93593402397924</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72190904862954</v>
+        <v>16.72696179343945</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0036451966402</v>
+        <v>102.0344669399806</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180477262157384</v>
+        <v>4.181740448359862</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.659194677906115</v>
+        <v>4.261766784135403</v>
       </c>
       <c r="C2" t="n">
-        <v>10.54397034361074</v>
+        <v>6.810383824360123</v>
       </c>
       <c r="D2" t="n">
-        <v>23.15844659547801</v>
+        <v>21.31766965001524</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.16371518689774</v>
+        <v>14.48568737616169</v>
       </c>
       <c r="C3" t="n">
-        <v>19.22752878767378</v>
+        <v>23.49322256262617</v>
       </c>
       <c r="D3" t="n">
-        <v>51.6939253671158</v>
+        <v>38.67104207028186</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.42105625859742</v>
+        <v>26.66132240423063</v>
       </c>
       <c r="C4" t="n">
-        <v>57.5853933403009</v>
+        <v>68.52304451331463</v>
       </c>
       <c r="D4" t="n">
-        <v>45.37147015176634</v>
+        <v>33.27241144462865</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.44047022850411</v>
+        <v>22.08932334555324</v>
       </c>
       <c r="C5" t="n">
-        <v>71.05399009486291</v>
+        <v>97.51209072431446</v>
       </c>
       <c r="D5" t="n">
-        <v>34.7538687303371</v>
+        <v>32.32404316232624</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.76606630894878</v>
+        <v>9.901907345033331</v>
       </c>
       <c r="C6" t="n">
-        <v>40.57366912111219</v>
+        <v>50.2340665309008</v>
       </c>
       <c r="D6" t="n">
-        <v>37.99756314516856</v>
+        <v>38.27932473628739</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5633,7 +5633,7 @@
         <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0373869887186</v>
+        <v>18.04433854169159</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6724770216404</v>
+        <v>117.7178276291309</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012462329572866</v>
+        <v>6.014779513897198</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.085273181549231</v>
+        <v>5.176755644493432</v>
       </c>
       <c r="C2" t="n">
-        <v>6.918376071827272</v>
+        <v>7.303221171892022</v>
       </c>
       <c r="D2" t="n">
-        <v>19.02627050830318</v>
+        <v>27.0255508025062</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76119862815655</v>
+        <v>12.88052987971815</v>
       </c>
       <c r="C3" t="n">
-        <v>29.51624472818035</v>
+        <v>23.59630607157209</v>
       </c>
       <c r="D3" t="n">
-        <v>54.37900533823083</v>
+        <v>43.53069320630357</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.81898287398687</v>
+        <v>19.73116535995239</v>
       </c>
       <c r="C4" t="n">
-        <v>43.73784197189966</v>
+        <v>52.74832240147687</v>
       </c>
       <c r="D4" t="n">
-        <v>52.54411887899354</v>
+        <v>38.84972015245478</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.50089661781091</v>
+        <v>18.8986433067511</v>
       </c>
       <c r="C5" t="n">
-        <v>66.04707680320418</v>
+        <v>83.05585577928017</v>
       </c>
       <c r="D5" t="n">
-        <v>34.36116964863837</v>
+        <v>29.550605897829</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.09437095279471</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>52.56866257159972</v>
+        <v>70.3196428120863</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>31.03402667894593</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>25.33203601268044</v>
+        <v>29.70375853969149</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5899,7 +5899,7 @@
         <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>31.89403766786613</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.045314351639916</v>
+        <v>7.048758670083934</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04982204662421</v>
+        <v>66.08211253203689</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403321469774947</v>
+        <v>4.405474168802459</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.159485096444488</v>
+        <v>4.520948178056562</v>
       </c>
       <c r="C2" t="n">
-        <v>7.42692138262712</v>
+        <v>8.015970005175207</v>
       </c>
       <c r="D2" t="n">
-        <v>24.80974623402114</v>
+        <v>24.06754496961056</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.40839134943345</v>
+        <v>16.03194001035041</v>
       </c>
       <c r="C3" t="n">
-        <v>27.92090470877929</v>
+        <v>27.00787934382975</v>
       </c>
       <c r="D3" t="n">
-        <v>57.22116494202534</v>
+        <v>55.71418221600649</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.6087499965578</v>
+        <v>23.24091340263474</v>
       </c>
       <c r="C4" t="n">
-        <v>62.0523453946239</v>
+        <v>56.25807044415922</v>
       </c>
       <c r="D4" t="n">
-        <v>68.85487523735006</v>
+        <v>52.27610175573416</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.15852871093603</v>
+        <v>25.05911015089984</v>
       </c>
       <c r="C5" t="n">
-        <v>75.25096153051803</v>
+        <v>92.08793465835082</v>
       </c>
       <c r="D5" t="n">
-        <v>45.77398671050754</v>
+        <v>37.74819922828986</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.32458294167398</v>
+        <v>19.32079481957723</v>
       </c>
       <c r="C6" t="n">
-        <v>83.48193428292329</v>
+        <v>106.7473913781642</v>
       </c>
       <c r="D6" t="n">
-        <v>35.70321876034376</v>
+        <v>33.93214590188251</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.81573453123786</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>54.85613472249477</v>
+        <v>71.50461229111218</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>27.53802310412303</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
         <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26368611684757</v>
+        <v>7.26761627138953</v>
       </c>
       <c r="C21" t="n">
-        <v>75.36074346229354</v>
+        <v>75.40151881566638</v>
       </c>
       <c r="D21" t="n">
-        <v>5.447764587635677</v>
+        <v>5.450712203542148</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.412375093512666</v>
+        <v>4.361905049968579</v>
       </c>
       <c r="C2" t="n">
-        <v>7.309111658117502</v>
+        <v>8.506843857298612</v>
       </c>
       <c r="D2" t="n">
-        <v>21.88021108454867</v>
+        <v>28.31262204277376</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.75062038758809</v>
+        <v>15.78159434576748</v>
       </c>
       <c r="C3" t="n">
-        <v>28.4854096387212</v>
+        <v>29.48188355853172</v>
       </c>
       <c r="D3" t="n">
-        <v>63.7890570834365</v>
+        <v>62.04154616987718</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.54341486872977</v>
+        <v>27.52918737478481</v>
       </c>
       <c r="C4" t="n">
-        <v>66.62139921018856</v>
+        <v>62.85639676440204</v>
       </c>
       <c r="D4" t="n">
-        <v>82.1025787584565</v>
+        <v>68.45923091253859</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.94517066394498</v>
+        <v>30.63052837250049</v>
       </c>
       <c r="C5" t="n">
-        <v>97.36482856867744</v>
+        <v>97.92933349861936</v>
       </c>
       <c r="D5" t="n">
-        <v>60.18113427032949</v>
+        <v>48.03200643027521</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.22649028670731</v>
+        <v>27.04911274740813</v>
       </c>
       <c r="C6" t="n">
-        <v>102.4002125437593</v>
+        <v>128.8858021089298</v>
       </c>
       <c r="D6" t="n">
-        <v>41.66046382971341</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.75691178444107</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="C7" t="n">
-        <v>90.8479873078871</v>
+        <v>116.7788894201581</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>51.90500112352886</v>
+        <v>65.17332134642452</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>33.62976760897448</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>34.02246669067321</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6619,7 +6619,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.468375814008119</v>
+        <v>7.473321498658889</v>
       </c>
       <c r="C21" t="n">
-        <v>84.01922790759133</v>
+        <v>84.0748668599125</v>
       </c>
       <c r="D21" t="n">
-        <v>6.534828837257104</v>
+        <v>6.539156311326527</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_18_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619922416</v>
+        <v>10.84497622195505</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907147850576</v>
+        <v>37.78907155771103</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.277875658030853</v>
+        <v>5.554728510628453</v>
       </c>
       <c r="C2" t="n">
-        <v>7.435757111965342</v>
+        <v>12.21195969312607</v>
       </c>
       <c r="D2" t="n">
-        <v>32.15616430490002</v>
+        <v>19.51812610813084</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.20236320026186</v>
+        <v>17.3278469799562</v>
       </c>
       <c r="C3" t="n">
-        <v>31.33247798103696</v>
+        <v>41.76845607718055</v>
       </c>
       <c r="D3" t="n">
-        <v>69.22303062644259</v>
+        <v>70.79873569175872</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.74164578952962</v>
+        <v>34.9953786655818</v>
       </c>
       <c r="C4" t="n">
-        <v>67.96148482648545</v>
+        <v>88.59880331745765</v>
       </c>
       <c r="D4" t="n">
-        <v>81.75798531426587</v>
+        <v>95.37580771987338</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.80924751240241</v>
+        <v>46.82936549257286</v>
       </c>
       <c r="C5" t="n">
-        <v>107.3295677667826</v>
+        <v>130.6460757426443</v>
       </c>
       <c r="D5" t="n">
-        <v>61.01561981893928</v>
+        <v>69.50773746067419</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.45541742824607</v>
+        <v>46.0478943199924</v>
       </c>
       <c r="C6" t="n">
-        <v>142.7323717296268</v>
+        <v>140.438027344802</v>
       </c>
       <c r="D6" t="n">
-        <v>44.07556318216056</v>
+        <v>48.18123208132072</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.3139636433765</v>
+        <v>34.31502750653876</v>
       </c>
       <c r="C7" t="n">
-        <v>150.8543704868606</v>
+        <v>116.2399099305266</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>17.85799074024948</v>
       </c>
       <c r="C8" t="n">
-        <v>110.0686438616311</v>
+        <v>75.18714792974197</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>55.35780779936488</v>
+        <v>42.71093387325747</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
         <v>34.87658719336794</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -954,7 +954,7 @@
         <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.663875262956981</v>
+        <v>7.660414302440445</v>
       </c>
       <c r="C21" t="n">
-        <v>92.92448756335338</v>
+        <v>93.84007520489544</v>
       </c>
       <c r="D21" t="n">
-        <v>7.663875262956981</v>
+        <v>7.660414302440445</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.494841900669398</v>
+        <v>6.821183049106838</v>
       </c>
       <c r="C2" t="n">
-        <v>9.205848222722341</v>
+        <v>10.03640678051514</v>
       </c>
       <c r="D2" t="n">
-        <v>25.50580535633214</v>
+        <v>23.98311466704533</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.42463909204914</v>
+        <v>17.7450897542611</v>
       </c>
       <c r="C3" t="n">
-        <v>29.91385254840031</v>
+        <v>44.29645641561608</v>
       </c>
       <c r="D3" t="n">
-        <v>77.02301613668351</v>
+        <v>69.5813685384927</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.39705234533899</v>
+        <v>33.54042856788804</v>
       </c>
       <c r="C4" t="n">
-        <v>72.88789480639595</v>
+        <v>95.12055331676922</v>
       </c>
       <c r="D4" t="n">
-        <v>95.29923139894213</v>
+        <v>105.1775767990735</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.8772090881737</v>
+        <v>49.60280275707011</v>
       </c>
       <c r="C5" t="n">
-        <v>114.594500778209</v>
+        <v>145.8386214658637</v>
       </c>
       <c r="D5" t="n">
-        <v>73.33655350723674</v>
+        <v>84.87208903213677</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.65417243286043</v>
+        <v>53.45419900083034</v>
       </c>
       <c r="C6" t="n">
-        <v>156.0556698239603</v>
+        <v>169.6204778535385</v>
       </c>
       <c r="D6" t="n">
-        <v>52.04539104523617</v>
+        <v>56.51332484726341</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.09922293805371</v>
+        <v>43.35790561035613</v>
       </c>
       <c r="C7" t="n">
-        <v>175.8270868397867</v>
+        <v>156.1243921632575</v>
       </c>
       <c r="D7" t="n">
-        <v>41.56130731158447</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.94282195344221</v>
+        <v>26.28629478120835</v>
       </c>
       <c r="C8" t="n">
-        <v>152.2101640664255</v>
+        <v>110.0686438616311</v>
       </c>
       <c r="D8" t="n">
-        <v>37.96909246174539</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>12.64687392610741</v>
       </c>
       <c r="C9" t="n">
-        <v>91.30155474724909</v>
+        <v>65.67499442329461</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>39.43189654107314</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
         <v>36.25005223160922</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.94134148411922</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
         <v>32.780555844801</v>
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.838530658840989</v>
+        <v>7.832279396344349</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9210822325777</v>
+        <v>101.8196321524765</v>
       </c>
       <c r="D21" t="n">
-        <v>8.818346991196112</v>
+        <v>8.811314320887393</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.848271074198249</v>
+        <v>7.375870502006286</v>
       </c>
       <c r="C2" t="n">
-        <v>15.38889526406875</v>
+        <v>10.86892883371644</v>
       </c>
       <c r="D2" t="n">
-        <v>22.41820882647592</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.94496537529995</v>
+        <v>19.49750940634166</v>
       </c>
       <c r="C3" t="n">
-        <v>32.27986451563513</v>
+        <v>41.49847545851267</v>
       </c>
       <c r="D3" t="n">
-        <v>78.15202599656735</v>
+        <v>71.16689108085129</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.94584931201296</v>
+        <v>32.72361447795468</v>
       </c>
       <c r="C4" t="n">
-        <v>72.73474216453344</v>
+        <v>100.493658502112</v>
       </c>
       <c r="D4" t="n">
-        <v>106.5942387363017</v>
+        <v>112.8734970526643</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.07985002587604</v>
+        <v>49.48008429403926</v>
       </c>
       <c r="C5" t="n">
-        <v>121.663084248786</v>
+        <v>156.3433219013046</v>
       </c>
       <c r="D5" t="n">
-        <v>86.93375921105508</v>
+        <v>97.24211010564659</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.76613272887356</v>
+        <v>58.64666260859173</v>
       </c>
       <c r="C6" t="n">
-        <v>167.5273917480843</v>
+        <v>195.5022925805971</v>
       </c>
       <c r="D6" t="n">
-        <v>60.01521890831177</v>
+        <v>66.85800040691205</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.5669768136317</v>
+        <v>51.86180422454201</v>
       </c>
       <c r="C7" t="n">
-        <v>196.0687610059475</v>
+        <v>191.277832209223</v>
       </c>
       <c r="D7" t="n">
-        <v>46.05280305851362</v>
+        <v>47.90928796724435</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.2849121228766</v>
+        <v>34.29735604786232</v>
       </c>
       <c r="C8" t="n">
-        <v>186.0902773399829</v>
+        <v>148.9556704268473</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>17.9718734739421</v>
       </c>
       <c r="C9" t="n">
-        <v>132.570301242968</v>
+        <v>94.18592950232622</v>
       </c>
       <c r="D9" t="n">
-        <v>36.60937189136354</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>8.683558444063038</v>
       </c>
       <c r="C10" t="n">
-        <v>71.60376880924112</v>
+        <v>55.23312584092555</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>41.5809422656694</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
         <v>36.78314123501524</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
         <v>33.30088212805181</v>
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.997667998287402</v>
+        <v>7.987122874658306</v>
       </c>
       <c r="C21" t="n">
-        <v>108.9682264766658</v>
+        <v>108.8245491672194</v>
       </c>
       <c r="D21" t="n">
-        <v>9.997084997859252</v>
+        <v>9.983903593322882</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.434955290710342</v>
+        <v>6.806456833543137</v>
       </c>
       <c r="C2" t="n">
-        <v>10.5871672425976</v>
+        <v>7.564366061221675</v>
       </c>
       <c r="D2" t="n">
-        <v>18.6846223072253</v>
+        <v>19.41406085148067</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.16509784522949</v>
+        <v>22.84526907782328</v>
       </c>
       <c r="C3" t="n">
-        <v>51.4190360099267</v>
+        <v>62.18389958699297</v>
       </c>
       <c r="D3" t="n">
-        <v>83.86579763528378</v>
+        <v>78.24038328994955</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.24618199405447</v>
+        <v>23.76418492899829</v>
       </c>
       <c r="C4" t="n">
-        <v>99.82999705404117</v>
+        <v>131.0986614343021</v>
       </c>
       <c r="D4" t="n">
-        <v>100.8254892261474</v>
+        <v>108.6235112409799</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.77087723647878</v>
+        <v>33.03581024790518</v>
       </c>
       <c r="C5" t="n">
-        <v>100.0891784479623</v>
+        <v>116.8034331127643</v>
       </c>
       <c r="D5" t="n">
-        <v>59.22393025868885</v>
+        <v>66.07162049581035</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.94973524510094</v>
+        <v>32.20132469929539</v>
       </c>
       <c r="C6" t="n">
-        <v>129.1273120441745</v>
+        <v>125.9876828859932</v>
       </c>
       <c r="D6" t="n">
-        <v>30.30949687321178</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>22.69702517448201</v>
       </c>
       <c r="C7" t="n">
-        <v>130.8522427605361</v>
+        <v>104.7416808183879</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>28.086820070797</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>12.43383467428585</v>
       </c>
       <c r="C8" t="n">
-        <v>97.71825774220626</v>
+        <v>69.42919764433444</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>54.58124536530566</v>
+        <v>42.15624642035802</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
         <v>28.75539025738908</v>
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
         <v>27.12078032981814</v>
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.281982575297087</v>
+        <v>4.276492999699106</v>
       </c>
       <c r="C2" t="n">
-        <v>5.089380098815464</v>
+        <v>3.830779541971054</v>
       </c>
       <c r="D2" t="n">
-        <v>13.07000718663779</v>
+        <v>13.89173001509237</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.98838325846506</v>
+        <v>23.6552109338269</v>
       </c>
       <c r="C3" t="n">
-        <v>47.33496556025997</v>
+        <v>46.76555189179681</v>
       </c>
       <c r="D3" t="n">
-        <v>81.13653901747765</v>
+        <v>77.04265109076846</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.19735665074939</v>
+        <v>32.08547847019426</v>
       </c>
       <c r="C4" t="n">
-        <v>115.8982617294487</v>
+        <v>147.19245155002</v>
       </c>
       <c r="D4" t="n">
-        <v>115.6047191658789</v>
+        <v>121.054400672153</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.27433388230815</v>
+        <v>36.20194659410114</v>
       </c>
       <c r="C5" t="n">
-        <v>139.8499604699582</v>
+        <v>172.1003725544659</v>
       </c>
       <c r="D5" t="n">
-        <v>75.91364123088462</v>
+        <v>81.77958376375932</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.41766904712818</v>
+        <v>37.43403996293088</v>
       </c>
       <c r="C6" t="n">
-        <v>147.522318778647</v>
+        <v>155.6934049210932</v>
       </c>
       <c r="D6" t="n">
-        <v>36.58875518957439</v>
+        <v>38.7220929509027</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.63040519931347</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>158.5198565616197</v>
+        <v>133.966346478407</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30262463928205</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>124.6721409623024</v>
+        <v>92.29410167624263</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>60.23905738488002</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.809761929554371</v>
+        <v>4.104687151455915</v>
       </c>
       <c r="C2" t="n">
-        <v>4.899902791895831</v>
+        <v>5.544911033585985</v>
       </c>
       <c r="D2" t="n">
-        <v>12.23650338573225</v>
+        <v>14.36984114706056</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.56070111231194</v>
+        <v>19.10481032464293</v>
       </c>
       <c r="C3" t="n">
-        <v>33.09962384868121</v>
+        <v>30.55689729468197</v>
       </c>
       <c r="D3" t="n">
-        <v>73.5329030480861</v>
+        <v>70.83309686140737</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.51941095547134</v>
+        <v>38.17329598422873</v>
       </c>
       <c r="C4" t="n">
-        <v>116.9192793418654</v>
+        <v>132.0813908862531</v>
       </c>
       <c r="D4" t="n">
-        <v>127.6399642722406</v>
+        <v>130.3073727846792</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.89483948912113</v>
+        <v>41.52792788964008</v>
       </c>
       <c r="C5" t="n">
-        <v>175.1928778228433</v>
+        <v>218.5861263505524</v>
       </c>
       <c r="D5" t="n">
-        <v>96.08855655315659</v>
+        <v>102.4699166307609</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.8453511932813</v>
+        <v>42.50574860306991</v>
       </c>
       <c r="C6" t="n">
-        <v>183.6683057536061</v>
+        <v>210.3954052540212</v>
       </c>
       <c r="D6" t="n">
-        <v>48.74475526355839</v>
+        <v>51.92463607761381</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.87668500435917</v>
+        <v>30.30262463928205</v>
       </c>
       <c r="C7" t="n">
-        <v>185.6484908730718</v>
+        <v>174.0903751509741</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>14.6034971006713</v>
       </c>
       <c r="C8" t="n">
-        <v>163.5591675275186</v>
+        <v>130.0962970282661</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>98.95624159726147</v>
+        <v>74.54999366968578</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>49.25428232206248</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>19.0517959486136</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.690569546713007</v>
+        <v>2.504438393533613</v>
       </c>
       <c r="C2" t="n">
-        <v>2.350304003966864</v>
+        <v>2.700787934382975</v>
       </c>
       <c r="D2" t="n">
-        <v>8.536296288426016</v>
+        <v>10.01677182643021</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.67712817848982</v>
+        <v>18.75628988963531</v>
       </c>
       <c r="C3" t="n">
-        <v>29.32480392585222</v>
+        <v>28.81920385816512</v>
       </c>
       <c r="D3" t="n">
-        <v>70.59747741238813</v>
+        <v>69.35065782799468</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.5952265128766</v>
+        <v>41.98934931063608</v>
       </c>
       <c r="C4" t="n">
-        <v>115.9237871697591</v>
+        <v>125.8404207303562</v>
       </c>
       <c r="D4" t="n">
-        <v>135.8463933320397</v>
+        <v>137.7608013553209</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.26928627506667</v>
+        <v>43.81049130201392</v>
       </c>
       <c r="C5" t="n">
-        <v>211.6893487282185</v>
+        <v>259.0095880729148</v>
       </c>
       <c r="D5" t="n">
-        <v>101.5863436969387</v>
+        <v>108.0167911597553</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.25037102677872</v>
+        <v>35.30070220160257</v>
       </c>
       <c r="C6" t="n">
-        <v>223.3161867896135</v>
+        <v>244.4885577794002</v>
       </c>
       <c r="D6" t="n">
-        <v>47.97997380195012</v>
+        <v>50.83784136901259</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.366053024963818</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>202.4167416616073</v>
+        <v>176.6056127692545</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>121.0004045484194</v>
+        <v>93.12858722485242</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>37.60780930658255</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.549598787928967</v>
+        <v>3.658973693727862</v>
       </c>
       <c r="C2" t="n">
-        <v>7.089200172366218</v>
+        <v>4.317726403277472</v>
       </c>
       <c r="D2" t="n">
-        <v>9.556332153138452</v>
+        <v>12.83144249450581</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.33289458719768</v>
+        <v>13.81319019875262</v>
       </c>
       <c r="C3" t="n">
-        <v>19.24225500323749</v>
+        <v>19.84602984134927</v>
       </c>
       <c r="D3" t="n">
-        <v>62.73367830137119</v>
+        <v>62.33116174262999</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.39178375391926</v>
+        <v>39.39851711912875</v>
       </c>
       <c r="C4" t="n">
-        <v>95.22265507801089</v>
+        <v>100.251166819163</v>
       </c>
       <c r="D4" t="n">
-        <v>139.0370733708418</v>
+        <v>140.0963791437241</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.87783098297945</v>
+        <v>51.71356032120075</v>
       </c>
       <c r="C5" t="n">
-        <v>214.2664364518664</v>
+        <v>248.7503245635356</v>
       </c>
       <c r="D5" t="n">
-        <v>121.4667347079366</v>
+        <v>127.3081335482052</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.17994723398021</v>
+        <v>44.03531152628644</v>
       </c>
       <c r="C6" t="n">
-        <v>274.5967963732414</v>
+        <v>317.4245582233043</v>
       </c>
       <c r="D6" t="n">
-        <v>63.27560303411543</v>
+        <v>67.62278186852032</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.09142570968197</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>257.153103164184</v>
+        <v>251.4638752180738</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>38.62686342359076</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>180.0819813899924</v>
+        <v>147.3701478844887</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>77.32343093418301</v>
+        <v>60.12811989430013</v>
       </c>
       <c r="D9" t="n">
         <v>32.39374724932775</v>
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.670934592628071</v>
+        <v>2.449460522095792</v>
       </c>
       <c r="C2" t="n">
-        <v>4.015348110369454</v>
+        <v>2.922662915542754</v>
       </c>
       <c r="D2" t="n">
-        <v>7.967864367667113</v>
+        <v>9.856746950637977</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.714393533522189</v>
+        <v>13.30268139254428</v>
       </c>
       <c r="C3" t="n">
-        <v>23.37541283811656</v>
+        <v>18.85446466005999</v>
       </c>
       <c r="D3" t="n">
-        <v>58.12437282993241</v>
+        <v>59.24356521277377</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.15456066239003</v>
+        <v>35.08471770666826</v>
       </c>
       <c r="C4" t="n">
-        <v>77.27827053978768</v>
+        <v>81.40062914992004</v>
       </c>
       <c r="D4" t="n">
-        <v>139.1391751320834</v>
+        <v>139.9177010615512</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.53484118129882</v>
+        <v>56.08233760509906</v>
       </c>
       <c r="C5" t="n">
-        <v>206.9524160552277</v>
+        <v>233.7786720737718</v>
       </c>
       <c r="D5" t="n">
-        <v>134.3276296335698</v>
+        <v>140.8807955594173</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.13719230334986</v>
+        <v>50.51582812201963</v>
       </c>
       <c r="C6" t="n">
-        <v>309.0924654573616</v>
+        <v>356.9919359475635</v>
       </c>
       <c r="D6" t="n">
-        <v>76.11588125795947</v>
+        <v>78.97374882502193</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.59426046070558</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="C7" t="n">
-        <v>310.2725261978662</v>
+        <v>318.3572185423387</v>
       </c>
       <c r="D7" t="n">
-        <v>42.39971985101125</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>224.893855350338</v>
+        <v>190.7633964121977</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>87.08593010521329</v>
+        <v>66.34061936677394</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3383,7 +3383,7 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.796999209399163</v>
+        <v>3.548036203147973</v>
       </c>
       <c r="C2" t="n">
-        <v>8.642325040484671</v>
+        <v>4.749695393146069</v>
       </c>
       <c r="D2" t="n">
-        <v>7.793113276311181</v>
+        <v>16.16840294124072</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.785259294677207</v>
+        <v>10.90721699418206</v>
       </c>
       <c r="C3" t="n">
-        <v>19.85584731839174</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="D3" t="n">
-        <v>52.20934291184538</v>
+        <v>54.42809272344316</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.59826956698058</v>
+        <v>30.33698580893068</v>
       </c>
       <c r="C4" t="n">
-        <v>68.85487523735006</v>
+        <v>66.64692465049897</v>
       </c>
       <c r="D4" t="n">
-        <v>136.6249192615074</v>
+        <v>137.5565978328376</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.3076565509903</v>
+        <v>55.17422097867075</v>
       </c>
       <c r="C5" t="n">
-        <v>179.6843735697725</v>
+        <v>199.2456965768902</v>
       </c>
       <c r="D5" t="n">
-        <v>148.1457285708437</v>
+        <v>151.2382338392212</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.50324532831367</v>
+        <v>58.68691426446584</v>
       </c>
       <c r="C6" t="n">
-        <v>317.8673264379196</v>
+        <v>363.7542141344155</v>
       </c>
       <c r="D6" t="n">
-        <v>93.10208003683779</v>
+        <v>96.9259873448791</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.21226279276233</v>
+        <v>31.02126395879071</v>
       </c>
       <c r="C7" t="n">
-        <v>364.3501349908932</v>
+        <v>393.275367601117</v>
       </c>
       <c r="D7" t="n">
-        <v>50.2448657556475</v>
+        <v>51.3228247349105</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.34347282776614</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>295.9085755370311</v>
+        <v>276.7988564738669</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -3677,10 +3677,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>156.4218617176442</v>
+        <v>123.1406145436774</v>
       </c>
       <c r="D9" t="n">
         <v>32.8374972116473</v>
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>56.37195317785186</v>
+        <v>46.40721397974673</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.597524498987813</v>
+        <v>8.298713343998289</v>
       </c>
       <c r="C2" t="n">
-        <v>12.63901994447344</v>
+        <v>8.464628706015999</v>
       </c>
       <c r="D2" t="n">
-        <v>10.43205110532661</v>
+        <v>15.85718891899448</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.019455027635689</v>
+        <v>2.592795686915826</v>
       </c>
       <c r="C2" t="n">
-        <v>4.977460860531329</v>
+        <v>2.812707172667112</v>
       </c>
       <c r="D2" t="n">
-        <v>5.797220193577415</v>
+        <v>12.02837287243192</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.68632376072653</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="C3" t="n">
-        <v>26.83116475706533</v>
+        <v>18.89373456822987</v>
       </c>
       <c r="D3" t="n">
-        <v>55.8319919405161</v>
+        <v>60.83890523217485</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.7956829709922</v>
+        <v>42.00211203079129</v>
       </c>
       <c r="C4" t="n">
-        <v>100.6468111439745</v>
+        <v>100.251166819163</v>
       </c>
       <c r="D4" t="n">
-        <v>140.4664980282251</v>
+        <v>140.3643962669835</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.1516154192773</v>
+        <v>33.55122779263475</v>
       </c>
       <c r="C5" t="n">
-        <v>269.416113737931</v>
+        <v>304.4645067795421</v>
       </c>
       <c r="D5" t="n">
-        <v>134.4748917892069</v>
+        <v>138.4264262988003</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.65789413503238</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="C6" t="n">
-        <v>299.1503064564541</v>
+        <v>323.1805450133033</v>
       </c>
       <c r="D6" t="n">
-        <v>74.38506005537235</v>
+        <v>76.27688788145595</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.850815406683489</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>208.1059696077176</v>
+        <v>194.6314823669302</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>31.79978988825843</v>
       </c>
     </row>
     <row r="8">
@@ -4285,10 +4285,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>115.2424542630118</v>
+        <v>90.70857913388404</v>
       </c>
       <c r="D8" t="n">
         <v>24.20008090968387</v>
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>43.04374634499714</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.855143308127976</v>
+        <v>7.327764864498192</v>
       </c>
       <c r="C2" t="n">
-        <v>10.00597260168349</v>
+        <v>4.538619636733004</v>
       </c>
       <c r="D2" t="n">
-        <v>10.64116336633118</v>
+        <v>14.87151422393068</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.773298395776997</v>
+        <v>17.61746255270901</v>
       </c>
       <c r="C3" t="n">
-        <v>31.84789552576653</v>
+        <v>21.32846887476196</v>
       </c>
       <c r="D3" t="n">
-        <v>11.89878217547134</v>
+        <v>16.45409152317654</v>
       </c>
     </row>
     <row r="4">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3972527197167</v>
+        <v>13.39640516330283</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1385583561639</v>
+        <v>70.13412114905596</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5761473787902</v>
+        <v>1.57604766627092</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.50622196249286</v>
+        <v>5.089380098815464</v>
       </c>
       <c r="C2" t="n">
-        <v>5.104106314379167</v>
+        <v>8.918196145378026</v>
       </c>
       <c r="D2" t="n">
-        <v>17.49965282819939</v>
+        <v>16.78984923802895</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.02212253330795</v>
+        <v>22.3003991019663</v>
       </c>
       <c r="C3" t="n">
-        <v>36.33448253417446</v>
+        <v>19.05572293943059</v>
       </c>
       <c r="D3" t="n">
-        <v>17.96107424919539</v>
+        <v>24.97075285751762</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.47368541953247</v>
+        <v>20.3310132072472</v>
       </c>
       <c r="C4" t="n">
-        <v>49.07265899677682</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D4" t="n">
-        <v>21.30097993904305</v>
+        <v>23.68760860806704</v>
       </c>
     </row>
     <row r="5">
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.438185717876</v>
+        <v>15.43693260151886</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12882558393979</v>
+        <v>86.12183451373683</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250144361658105</v>
+        <v>3.249880547688182</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.926009069282995</v>
+        <v>5.426119561372121</v>
       </c>
       <c r="C2" t="n">
-        <v>5.479133937401449</v>
+        <v>6.253732876052181</v>
       </c>
       <c r="D2" t="n">
-        <v>22.45060650071606</v>
+        <v>28.17517736417921</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.79141182280995</v>
+        <v>19.66440651606361</v>
       </c>
       <c r="C3" t="n">
-        <v>26.48755306057895</v>
+        <v>28.72593782626167</v>
       </c>
       <c r="D3" t="n">
-        <v>27.7932775072272</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.56448923440869</v>
+        <v>33.37451320587032</v>
       </c>
       <c r="C4" t="n">
-        <v>72.84960664593032</v>
+        <v>41.22358610132357</v>
       </c>
       <c r="D4" t="n">
-        <v>25.52544031041707</v>
+        <v>30.87302005544944</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.35743827980385</v>
+        <v>17.18058482431918</v>
       </c>
       <c r="C5" t="n">
-        <v>54.02066742618075</v>
+        <v>37.15915060574178</v>
       </c>
       <c r="D5" t="n">
-        <v>30.31146036862028</v>
+        <v>31.17048960983623</v>
       </c>
     </row>
     <row r="6">
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.01453059358123</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5319,7 +5319,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72696179343945</v>
+        <v>16.72668970182433</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0344669399806</v>
+        <v>102.0328071811284</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181740448359862</v>
+        <v>4.181672425456084</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.261766784135403</v>
+        <v>5.602834148136546</v>
       </c>
       <c r="C2" t="n">
-        <v>6.810383824360123</v>
+        <v>11.23119373658351</v>
       </c>
       <c r="D2" t="n">
-        <v>21.31766965001524</v>
+        <v>24.31789063419349</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.48568737616169</v>
+        <v>19.03117924682442</v>
       </c>
       <c r="C3" t="n">
-        <v>23.49322256262617</v>
+        <v>26.1635763181775</v>
       </c>
       <c r="D3" t="n">
-        <v>38.67104207028186</v>
+        <v>46.76555189179681</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.66132240423063</v>
+        <v>35.67180283380785</v>
       </c>
       <c r="C4" t="n">
-        <v>68.52304451331463</v>
+        <v>57.63644422092175</v>
       </c>
       <c r="D4" t="n">
-        <v>33.27241144462865</v>
+        <v>39.75587328347459</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.08932334555324</v>
+        <v>33.64940256305943</v>
       </c>
       <c r="C5" t="n">
-        <v>97.51209072431446</v>
+        <v>58.21763886183587</v>
       </c>
       <c r="D5" t="n">
-        <v>32.32404316232624</v>
+        <v>34.77841242294326</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.901907345033331</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>50.2340665309008</v>
+        <v>36.4277485660779</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>38.56108632740622</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>20.90042687571034</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
         <v>31.46010518258904</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
         <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04433854169159</v>
+        <v>18.04529479093201</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7178276291309</v>
+        <v>117.7240660170326</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014779513897198</v>
+        <v>6.015098263644004</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.176755644493432</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C2" t="n">
-        <v>7.303221171892022</v>
+        <v>9.559277396251192</v>
       </c>
       <c r="D2" t="n">
-        <v>27.0255508025062</v>
+        <v>29.14318060056657</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.88052987971815</v>
+        <v>17.14622365467055</v>
       </c>
       <c r="C3" t="n">
-        <v>23.59630607157209</v>
+        <v>33.76721228756904</v>
       </c>
       <c r="D3" t="n">
-        <v>43.53069320630357</v>
+        <v>51.60065933521236</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.73116535995239</v>
+        <v>26.12528815771187</v>
       </c>
       <c r="C4" t="n">
-        <v>52.74832240147687</v>
+        <v>51.31889774409352</v>
       </c>
       <c r="D4" t="n">
-        <v>38.84972015245478</v>
+        <v>46.66050488744241</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.8986433067511</v>
+        <v>26.5808190924824</v>
       </c>
       <c r="C5" t="n">
-        <v>83.05585577928017</v>
+        <v>62.46369768270332</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>32.86400439966199</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.86794708601219</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="C6" t="n">
-        <v>70.3196428120863</v>
+        <v>44.1560664939088</v>
       </c>
       <c r="D6" t="n">
-        <v>31.03402667894593</v>
+        <v>31.71830482880595</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>29.70375853969149</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
         <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.39687241888974</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5910,10 +5910,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5955,7 +5955,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.048758670083934</v>
+        <v>7.049578075989958</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08211253203689</v>
+        <v>66.9709917219046</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405474168802459</v>
+        <v>4.405986297493723</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.520948178056562</v>
+        <v>5.028511741152163</v>
       </c>
       <c r="C2" t="n">
-        <v>8.015970005175207</v>
+        <v>9.957866964175397</v>
       </c>
       <c r="D2" t="n">
-        <v>24.06754496961056</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.03194001035041</v>
+        <v>19.71349390127595</v>
       </c>
       <c r="C3" t="n">
-        <v>27.00787934382975</v>
+        <v>36.0252320073367</v>
       </c>
       <c r="D3" t="n">
-        <v>55.71418221600649</v>
+        <v>63.61234249667208</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.24091340263474</v>
+        <v>30.87302005544944</v>
       </c>
       <c r="C4" t="n">
-        <v>56.25807044415922</v>
+        <v>71.95621623506572</v>
       </c>
       <c r="D4" t="n">
-        <v>52.27610175573416</v>
+        <v>62.88192220471245</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.05911015089984</v>
+        <v>33.91938318172731</v>
       </c>
       <c r="C5" t="n">
-        <v>92.08793465835082</v>
+        <v>81.41142837466676</v>
       </c>
       <c r="D5" t="n">
-        <v>37.74819922828986</v>
+        <v>42.46058820867456</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.32079481957723</v>
+        <v>27.73339089726815</v>
       </c>
       <c r="C6" t="n">
-        <v>106.7473913781642</v>
+        <v>76.5989011284489</v>
       </c>
       <c r="D6" t="n">
-        <v>33.93214590188251</v>
+        <v>35.50196048097316</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>13.77392029058275</v>
       </c>
       <c r="C7" t="n">
-        <v>71.50461229111218</v>
+        <v>46.95110220789945</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>30.79251674370121</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
         <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26761627138953</v>
+        <v>7.26784429893288</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40151881566638</v>
+        <v>76.31236513879524</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450712203542148</v>
+        <v>5.45088322419966</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.361905049968579</v>
+        <v>4.860632883725958</v>
       </c>
       <c r="C2" t="n">
-        <v>8.506843857298612</v>
+        <v>11.69556040069225</v>
       </c>
       <c r="D2" t="n">
-        <v>28.31262204277376</v>
+        <v>22.61063137650829</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.78159434576748</v>
+        <v>18.38813450054276</v>
       </c>
       <c r="C3" t="n">
-        <v>29.48188355853172</v>
+        <v>37.62548076525901</v>
       </c>
       <c r="D3" t="n">
-        <v>62.04154616987718</v>
+        <v>69.26230053461248</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.52918737478481</v>
+        <v>35.16129402759952</v>
       </c>
       <c r="C4" t="n">
-        <v>62.85639676440204</v>
+        <v>82.5365112437336</v>
       </c>
       <c r="D4" t="n">
-        <v>68.45923091253859</v>
+        <v>80.64762866076273</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.63052837250049</v>
+        <v>40.49709280018094</v>
       </c>
       <c r="C5" t="n">
-        <v>97.92933349861936</v>
+        <v>110.3238982647353</v>
       </c>
       <c r="D5" t="n">
-        <v>48.03200643027521</v>
+        <v>55.4687452899448</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.04911274740813</v>
+        <v>37.71580155404972</v>
       </c>
       <c r="C6" t="n">
-        <v>128.8858021089298</v>
+        <v>105.2178284549477</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>40.53341746523807</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.76825078853552</v>
+        <v>23.77498415374501</v>
       </c>
       <c r="C7" t="n">
-        <v>116.7788894201581</v>
+        <v>80.6073770048886</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>65.17332134642452</v>
+        <v>45.64635950895544</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>31.39530983410874</v>
+        <v>28.6218725696115</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
         <v>34.02246669067321</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6546,10 +6546,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.473321498658889</v>
+        <v>7.472035355207384</v>
       </c>
       <c r="C21" t="n">
-        <v>84.0748668599125</v>
+        <v>84.99440216548399</v>
       </c>
       <c r="D21" t="n">
-        <v>6.539156311326527</v>
+        <v>6.538030935806462</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_18_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_18_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497622195505</v>
+        <v>10.84497626337147</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907155771103</v>
+        <v>37.78907170202558</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.554728510628453</v>
+        <v>1.052433538952581</v>
       </c>
       <c r="C2" t="n">
-        <v>12.21195969312607</v>
+        <v>2.332632545290422</v>
       </c>
       <c r="D2" t="n">
-        <v>19.51812610813084</v>
+        <v>15.94161922155971</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.3278469799562</v>
+        <v>9.356055621472104</v>
       </c>
       <c r="C3" t="n">
-        <v>41.76845607718055</v>
+        <v>25.77578597500001</v>
       </c>
       <c r="D3" t="n">
-        <v>70.79873569175872</v>
+        <v>91.75904917742814</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.9953786655818</v>
+        <v>16.20865459711484</v>
       </c>
       <c r="C4" t="n">
-        <v>88.59880331745765</v>
+        <v>79.53727200725959</v>
       </c>
       <c r="D4" t="n">
-        <v>95.37580771987338</v>
+        <v>116.2428551736393</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.82936549257286</v>
+        <v>14.89802141194535</v>
       </c>
       <c r="C5" t="n">
-        <v>130.6460757426443</v>
+        <v>83.79216655746528</v>
       </c>
       <c r="D5" t="n">
-        <v>69.50773746067419</v>
+        <v>65.92435834017333</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.0478943199924</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="C6" t="n">
-        <v>140.438027344802</v>
+        <v>53.41394734495622</v>
       </c>
       <c r="D6" t="n">
-        <v>48.18123208132072</v>
+        <v>31.5975498611836</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.31502750653876</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>116.2399099305266</v>
+        <v>34.37491411649782</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.85799074024948</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>75.18714792974197</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.85539932116455</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.660414302440445</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.84007520489544</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.660414302440445</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.821183049106838</v>
+        <v>0.6980226177194822</v>
       </c>
       <c r="C2" t="n">
-        <v>10.03640678051514</v>
+        <v>4.149847545851268</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98311466704533</v>
+        <v>16.47765346807846</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7450897542611</v>
+        <v>6.243915399009714</v>
       </c>
       <c r="C3" t="n">
-        <v>44.29645641561608</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D3" t="n">
-        <v>69.5813685384927</v>
+        <v>84.10141708430302</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.54042856788804</v>
+        <v>17.47216389248048</v>
       </c>
       <c r="C4" t="n">
-        <v>95.12055331676922</v>
+        <v>71.0245376637355</v>
       </c>
       <c r="D4" t="n">
-        <v>105.1775767990735</v>
+        <v>135.0168165219511</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.60280275707011</v>
+        <v>19.92947839621025</v>
       </c>
       <c r="C5" t="n">
-        <v>145.8386214658637</v>
+        <v>119.355977143806</v>
       </c>
       <c r="D5" t="n">
-        <v>84.87208903213677</v>
+        <v>91.15527433931635</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.45419900083034</v>
+        <v>15.21512592041707</v>
       </c>
       <c r="C6" t="n">
-        <v>169.6204778535385</v>
+        <v>95.27566945404023</v>
       </c>
       <c r="D6" t="n">
-        <v>56.51332484726341</v>
+        <v>43.63279496754524</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.35790561035613</v>
+        <v>9.102764713776425</v>
       </c>
       <c r="C7" t="n">
-        <v>156.1243921632575</v>
+        <v>56.2934133615121</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6573386601514</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.28629478120835</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>110.0686438616311</v>
+        <v>37.30150402285756</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>65.67499442329461</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>46.94128473085699</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.832279396344349</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.8196321524765</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.811314320887393</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.375870502006286</v>
+        <v>0.3652101459798134</v>
       </c>
       <c r="C2" t="n">
-        <v>10.86892883371644</v>
+        <v>1.709222753093697</v>
       </c>
       <c r="D2" t="n">
-        <v>23.41468274628643</v>
+        <v>11.16836188351171</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.49750940634166</v>
+        <v>5.232715263635499</v>
       </c>
       <c r="C3" t="n">
-        <v>41.49847545851267</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="D3" t="n">
-        <v>71.16689108085129</v>
+        <v>81.59305169995241</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.72361447795468</v>
+        <v>19.08026663203676</v>
       </c>
       <c r="C4" t="n">
-        <v>100.493658502112</v>
+        <v>65.23026271327082</v>
       </c>
       <c r="D4" t="n">
-        <v>112.8734970526643</v>
+        <v>147.0265361880023</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.48008429403926</v>
+        <v>20.00310947402876</v>
       </c>
       <c r="C5" t="n">
-        <v>156.3433219013046</v>
+        <v>138.8436690731052</v>
       </c>
       <c r="D5" t="n">
-        <v>97.24211010564659</v>
+        <v>104.801567428347</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.64666260859173</v>
+        <v>12.47801332097696</v>
       </c>
       <c r="C6" t="n">
-        <v>195.5022925805971</v>
+        <v>125.5449146713779</v>
       </c>
       <c r="D6" t="n">
-        <v>66.85800040691205</v>
+        <v>43.71329827929349</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.86180422454201</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>191.277832209223</v>
+        <v>57.31148573081605</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.29735604786232</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>148.9556704268473</v>
+        <v>38.97047512007713</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.9718734739421</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>94.18592950232622</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>55.23312584092555</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.49392657288993</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.66398990990288</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.987122874658306</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108.8245491672194</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.983903593322882</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.806456833543137</v>
+        <v>0.8717919613711677</v>
       </c>
       <c r="C2" t="n">
-        <v>7.564366061221675</v>
+        <v>3.633448253417445</v>
       </c>
       <c r="D2" t="n">
-        <v>19.41406085148067</v>
+        <v>13.12793030118835</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.84526907782328</v>
+        <v>3.136683915068559</v>
       </c>
       <c r="C3" t="n">
-        <v>62.18389958699297</v>
+        <v>11.10356653503143</v>
       </c>
       <c r="D3" t="n">
-        <v>78.24038328994955</v>
+        <v>71.9326542901638</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.76418492899829</v>
+        <v>14.8047553800419</v>
       </c>
       <c r="C4" t="n">
-        <v>131.0986614343021</v>
+        <v>53.28435664799564</v>
       </c>
       <c r="D4" t="n">
-        <v>108.6235112409799</v>
+        <v>155.8328130950962</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.03581024790518</v>
+        <v>24.44551783574558</v>
       </c>
       <c r="C5" t="n">
-        <v>116.8034331127643</v>
+        <v>130.449726201795</v>
       </c>
       <c r="D5" t="n">
-        <v>66.07162049581035</v>
+        <v>130.6460757426443</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.20132469929539</v>
+        <v>19.0390332284584</v>
       </c>
       <c r="C6" t="n">
-        <v>125.9876828859932</v>
+        <v>175.6984778905305</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>62.792583163626</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.69702517448201</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>104.7416808183879</v>
+        <v>116.7788894201581</v>
       </c>
       <c r="D7" t="n">
-        <v>28.086820070797</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.43383467428585</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>69.42919764433444</v>
+        <v>56.4946716408827</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.17187226816798</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>31.24313893995049</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.276492999699106</v>
+        <v>0.5006913291658733</v>
       </c>
       <c r="C2" t="n">
-        <v>3.830779541971054</v>
+        <v>1.769109363052752</v>
       </c>
       <c r="D2" t="n">
-        <v>13.89173001509237</v>
+        <v>9.717338776634929</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6552109338269</v>
+        <v>3.136683915068559</v>
       </c>
       <c r="C3" t="n">
-        <v>46.76555189179681</v>
+        <v>12.88543861823939</v>
       </c>
       <c r="D3" t="n">
-        <v>77.04265109076846</v>
+        <v>66.9306497370263</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.08547847019426</v>
+        <v>11.57578718077414</v>
       </c>
       <c r="C4" t="n">
-        <v>147.19245155002</v>
+        <v>41.98934931063608</v>
       </c>
       <c r="D4" t="n">
-        <v>121.054400672153</v>
+        <v>157.3771022338764</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.20194659410114</v>
+        <v>25.30454707696154</v>
       </c>
       <c r="C5" t="n">
-        <v>172.1003725544659</v>
+        <v>120.656792851933</v>
       </c>
       <c r="D5" t="n">
-        <v>81.77958376375932</v>
+        <v>151.8763698469816</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="C6" t="n">
-        <v>155.6934049210932</v>
+        <v>198.8834316740231</v>
       </c>
       <c r="D6" t="n">
-        <v>38.7220929509027</v>
+        <v>79.21525876026665</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.31963314542373</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>133.966346478407</v>
+        <v>168.6406936447001</v>
       </c>
       <c r="D7" t="n">
-        <v>30.54217107911827</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>92.29410167624263</v>
+        <v>84.86718029361552</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>47.25937098703294</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.104687151455915</v>
+        <v>1.271363276999619</v>
       </c>
       <c r="C2" t="n">
-        <v>5.544911033585985</v>
+        <v>12.49175778883641</v>
       </c>
       <c r="D2" t="n">
-        <v>14.36984114706056</v>
+        <v>10.00989959250048</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.10481032464293</v>
+        <v>2.41019061392592</v>
       </c>
       <c r="C3" t="n">
-        <v>30.55689729468197</v>
+        <v>9.616218763097507</v>
       </c>
       <c r="D3" t="n">
-        <v>70.83309686140737</v>
+        <v>60.32348768744527</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.17329598422873</v>
+        <v>8.831802347404306</v>
       </c>
       <c r="C4" t="n">
-        <v>132.0813908862531</v>
+        <v>36.87149852839745</v>
       </c>
       <c r="D4" t="n">
-        <v>130.3073727846792</v>
+        <v>153.7907778702628</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.52792788964008</v>
+        <v>22.31021657900877</v>
       </c>
       <c r="C5" t="n">
-        <v>218.5861263505524</v>
+        <v>100.1382658331747</v>
       </c>
       <c r="D5" t="n">
-        <v>102.4699166307609</v>
+        <v>171.8549356284042</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.50574860306991</v>
+        <v>28.41766904712818</v>
       </c>
       <c r="C6" t="n">
-        <v>210.3954052540212</v>
+        <v>196.468332321576</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>104.2115370580947</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.30262463928205</v>
+        <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>174.0903751509741</v>
+        <v>226.3114990352705</v>
       </c>
       <c r="D7" t="n">
-        <v>33.89582123682538</v>
+        <v>54.25726862290422</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.6034971006713</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>130.0962970282661</v>
+        <v>147.4535964393497</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>42.89255719854314</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>74.54999366968578</v>
+        <v>72.66405632982764</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>42.71093387325747</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>42.84837855185204</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>42.15820991576653</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.504438393533613</v>
+        <v>0.8433212779480102</v>
       </c>
       <c r="C2" t="n">
-        <v>2.700787934382975</v>
+        <v>6.396086293167969</v>
       </c>
       <c r="D2" t="n">
-        <v>10.01677182643021</v>
+        <v>7.207009896875835</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.75628988963531</v>
+        <v>3.814089830998858</v>
       </c>
       <c r="C3" t="n">
-        <v>28.81920385816512</v>
+        <v>25.46162670964103</v>
       </c>
       <c r="D3" t="n">
-        <v>69.35065782799468</v>
+        <v>63.60252501962961</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.98934931063608</v>
+        <v>14.94514530174919</v>
       </c>
       <c r="C4" t="n">
-        <v>125.8404207303562</v>
+        <v>52.44201711775187</v>
       </c>
       <c r="D4" t="n">
-        <v>137.7608013553209</v>
+        <v>162.1120714114588</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.81049130201392</v>
+        <v>17.84326452468578</v>
       </c>
       <c r="C5" t="n">
-        <v>259.0095880729148</v>
+        <v>157.7913997650686</v>
       </c>
       <c r="D5" t="n">
-        <v>108.0167911597553</v>
+        <v>158.5522542358599</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.30070220160257</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="C6" t="n">
-        <v>244.4885577794002</v>
+        <v>201.0167694353514</v>
       </c>
       <c r="D6" t="n">
-        <v>50.83784136901259</v>
+        <v>83.48193428292329</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>176.6056127692545</v>
+        <v>103.6637218391249</v>
       </c>
       <c r="D7" t="n">
-        <v>34.13536767666159</v>
+        <v>38.08788393395925</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>93.12858722485242</v>
+        <v>53.49052366588747</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.47545329295849</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.658973693727862</v>
+        <v>0.3877903431774901</v>
       </c>
       <c r="C2" t="n">
-        <v>4.317726403277472</v>
+        <v>2.73318560862312</v>
       </c>
       <c r="D2" t="n">
-        <v>12.83144249450581</v>
+        <v>5.808019418324131</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.81319019875262</v>
+        <v>3.342850932960389</v>
       </c>
       <c r="C3" t="n">
-        <v>19.84602984134927</v>
+        <v>25.25545969174919</v>
       </c>
       <c r="D3" t="n">
-        <v>62.33116174262999</v>
+        <v>55.07113746972483</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.39851711912875</v>
+        <v>10.42714236680537</v>
       </c>
       <c r="C4" t="n">
-        <v>100.251166819163</v>
+        <v>56.61542660850506</v>
       </c>
       <c r="D4" t="n">
-        <v>140.0963791437241</v>
+        <v>151.4041492012389</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.71356032120075</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C5" t="n">
-        <v>248.7503245635356</v>
+        <v>114.7172192412398</v>
       </c>
       <c r="D5" t="n">
-        <v>127.3081335482052</v>
+        <v>161.153885652114</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.03531152628644</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>317.4245582233043</v>
+        <v>188.4180011467521</v>
       </c>
       <c r="D6" t="n">
-        <v>67.62278186852032</v>
+        <v>92.25679526348128</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>251.4638752180738</v>
+        <v>136.4815840966873</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>147.3701478844887</v>
+        <v>59.58226817073891</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>60.12811989430013</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>18.79065105928395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>13.68261775408779</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.449460522095792</v>
+        <v>0.2532909076956771</v>
       </c>
       <c r="C2" t="n">
-        <v>2.922662915542754</v>
+        <v>3.855323234577225</v>
       </c>
       <c r="D2" t="n">
-        <v>9.856746950637977</v>
+        <v>16.94692887070844</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.30268139254428</v>
+        <v>2.238384765682727</v>
       </c>
       <c r="C3" t="n">
-        <v>18.85446466005999</v>
+        <v>16.49827016986765</v>
       </c>
       <c r="D3" t="n">
-        <v>59.24356521277377</v>
+        <v>46.93735774004001</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.08471770666826</v>
+        <v>8.346818981506383</v>
       </c>
       <c r="C4" t="n">
-        <v>81.40062914992004</v>
+        <v>60.5591071364645</v>
       </c>
       <c r="D4" t="n">
-        <v>139.9177010615512</v>
+        <v>145.2142299259627</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.08233760509906</v>
+        <v>16.41973035352791</v>
       </c>
       <c r="C5" t="n">
-        <v>233.7786720737718</v>
+        <v>110.2257234943107</v>
       </c>
       <c r="D5" t="n">
-        <v>140.8807955594173</v>
+        <v>179.9543541884404</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.51582812201963</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="C6" t="n">
-        <v>356.9919359475635</v>
+        <v>186.1236567619273</v>
       </c>
       <c r="D6" t="n">
-        <v>78.97374882502193</v>
+        <v>120.6744643106095</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>318.3572185423387</v>
+        <v>211.0404134957113</v>
       </c>
       <c r="D7" t="n">
-        <v>43.05847256056086</v>
+        <v>55.15556777229006</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>190.7633964121977</v>
+        <v>122.8362727553609</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>66.34061936677394</v>
+        <v>52.25155806312797</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.548036203147973</v>
+        <v>0.3946625771072178</v>
       </c>
       <c r="C2" t="n">
-        <v>4.749695393146069</v>
+        <v>5.664684253504096</v>
       </c>
       <c r="D2" t="n">
-        <v>16.16840294124072</v>
+        <v>18.18883971658066</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.90721699418206</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C3" t="n">
-        <v>15.52143120414207</v>
+        <v>15.60487975900305</v>
       </c>
       <c r="D3" t="n">
-        <v>54.42809272344316</v>
+        <v>49.82860472904687</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.33698580893068</v>
+        <v>6.279258316362599</v>
       </c>
       <c r="C4" t="n">
-        <v>66.64692465049897</v>
+        <v>49.96604940764141</v>
       </c>
       <c r="D4" t="n">
-        <v>137.5565978328376</v>
+        <v>135.3996981266073</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.17422097867075</v>
+        <v>14.67712817848982</v>
       </c>
       <c r="C5" t="n">
-        <v>199.2456965768902</v>
+        <v>111.0847527355266</v>
       </c>
       <c r="D5" t="n">
-        <v>151.2382338392212</v>
+        <v>191.6371518689774</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.68691426446584</v>
+        <v>19.60255641069606</v>
       </c>
       <c r="C6" t="n">
-        <v>363.7542141344155</v>
+        <v>181.4947163364036</v>
       </c>
       <c r="D6" t="n">
-        <v>96.9259873448791</v>
+        <v>147.4820671227729</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.02126395879071</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>393.275367601117</v>
+        <v>242.5407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>51.3228247349105</v>
+        <v>73.54075702972007</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>276.7988564738669</v>
+        <v>201.611708544125</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>123.1406145436774</v>
+        <v>101.1749914088593</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>25.84843530511426</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>46.40721397974673</v>
+        <v>43.84485247166256</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.298713343998289</v>
+        <v>3.681553890925539</v>
       </c>
       <c r="C2" t="n">
-        <v>8.464628706015999</v>
+        <v>6.66704865954009</v>
       </c>
       <c r="D2" t="n">
-        <v>15.85718891899448</v>
+        <v>20.31137825316226</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.592795686915826</v>
+        <v>0.2964878066825367</v>
       </c>
       <c r="C2" t="n">
-        <v>2.812707172667112</v>
+        <v>9.200939484201108</v>
       </c>
       <c r="D2" t="n">
-        <v>12.02837287243192</v>
+        <v>21.38933723242526</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.44641746799181</v>
+        <v>1.413716694115407</v>
       </c>
       <c r="C3" t="n">
-        <v>18.89373456822987</v>
+        <v>18.81519475189012</v>
       </c>
       <c r="D3" t="n">
-        <v>60.83890523217485</v>
+        <v>52.0669894947296</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.00211203079129</v>
+        <v>4.569053815564656</v>
       </c>
       <c r="C4" t="n">
-        <v>100.251166819163</v>
+        <v>44.4142661401257</v>
       </c>
       <c r="D4" t="n">
-        <v>140.3643962669835</v>
+        <v>130.3201355048344</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.55122779263475</v>
+        <v>12.51728322914684</v>
       </c>
       <c r="C5" t="n">
-        <v>304.4645067795421</v>
+        <v>101.8563243156066</v>
       </c>
       <c r="D5" t="n">
-        <v>138.4264262988003</v>
+        <v>194.5087639038994</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.24029150782899</v>
+        <v>19.84406634594078</v>
       </c>
       <c r="C6" t="n">
-        <v>323.1805450133033</v>
+        <v>178.2745838664741</v>
       </c>
       <c r="D6" t="n">
-        <v>76.27688788145595</v>
+        <v>171.1097891208809</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="C7" t="n">
-        <v>194.6314823669302</v>
+        <v>254.5180923259856</v>
       </c>
       <c r="D7" t="n">
-        <v>31.79978988825843</v>
+        <v>93.48299814608552</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="C8" t="n">
-        <v>90.70857913388404</v>
+        <v>258.9408657336174</v>
       </c>
       <c r="D8" t="n">
-        <v>24.20008090968387</v>
+        <v>47.14843349645307</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>35.38905949498476</v>
+        <v>167.1827983038935</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>77.44025891098842</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>19.72429312602266</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.327764864498192</v>
+        <v>4.436517875491336</v>
       </c>
       <c r="C2" t="n">
-        <v>4.538619636733004</v>
+        <v>6.096653243372693</v>
       </c>
       <c r="D2" t="n">
-        <v>14.87151422393068</v>
+        <v>36.05468443846411</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.61746255270901</v>
+        <v>5.944482349214437</v>
       </c>
       <c r="C3" t="n">
-        <v>21.32846887476196</v>
+        <v>13.16032797542849</v>
       </c>
       <c r="D3" t="n">
-        <v>16.45409152317654</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39640516330283</v>
+        <v>11.67724933622482</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13412114905596</v>
+        <v>59.94321325928741</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57604766627092</v>
+        <v>0.7784832890816547</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.089380098815464</v>
+        <v>2.382701678207009</v>
       </c>
       <c r="C2" t="n">
-        <v>8.918196145378026</v>
+        <v>2.856885819358218</v>
       </c>
       <c r="D2" t="n">
-        <v>16.78984923802895</v>
+        <v>37.35157315577415</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.3003991019663</v>
+        <v>11.90859965251381</v>
       </c>
       <c r="C3" t="n">
-        <v>19.05572293943059</v>
+        <v>20.15528036818702</v>
       </c>
       <c r="D3" t="n">
-        <v>24.97075285751762</v>
+        <v>44.31609136970102</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.3310132072472</v>
+        <v>7.478954010952201</v>
       </c>
       <c r="C4" t="n">
-        <v>33.0554452019901</v>
+        <v>21.64557338323367</v>
       </c>
       <c r="D4" t="n">
-        <v>23.68760860806704</v>
+        <v>23.22815068247953</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43693260151886</v>
+        <v>13.62538680472999</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12183451373683</v>
+        <v>73.73738741383288</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249880547688182</v>
+        <v>1.60298668290941</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.426119561372121</v>
+        <v>1.579632056133118</v>
       </c>
       <c r="C2" t="n">
-        <v>6.253732876052181</v>
+        <v>5.708862900195202</v>
       </c>
       <c r="D2" t="n">
-        <v>28.17517736417921</v>
+        <v>31.52097354025234</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.66440651606361</v>
+        <v>9.822385780989338</v>
       </c>
       <c r="C3" t="n">
-        <v>28.72593782626167</v>
+        <v>14.43659999094935</v>
       </c>
       <c r="D3" t="n">
-        <v>32.6087499965578</v>
+        <v>64.98188054409637</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.37451320587032</v>
+        <v>16.8978414854961</v>
       </c>
       <c r="C4" t="n">
-        <v>41.22358610132357</v>
+        <v>39.50061888037042</v>
       </c>
       <c r="D4" t="n">
-        <v>30.87302005544944</v>
+        <v>41.05767073930586</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.18058482431918</v>
+        <v>7.289476704032569</v>
       </c>
       <c r="C5" t="n">
-        <v>37.15915060574178</v>
+        <v>26.04085785514665</v>
       </c>
       <c r="D5" t="n">
-        <v>31.17048960983623</v>
+        <v>28.32342126752049</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72668970182433</v>
+        <v>14.83211277384619</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0328071811284</v>
+        <v>87.34466411264977</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181672425456084</v>
+        <v>2.472018795641031</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.602834148136546</v>
+        <v>1.912444527872786</v>
       </c>
       <c r="C2" t="n">
-        <v>11.23119373658351</v>
+        <v>5.219952543480291</v>
       </c>
       <c r="D2" t="n">
-        <v>24.31789063419349</v>
+        <v>27.63816136995621</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.03117924682442</v>
+        <v>7.363107781851078</v>
       </c>
       <c r="C3" t="n">
-        <v>26.1635763181775</v>
+        <v>19.15389770985527</v>
       </c>
       <c r="D3" t="n">
-        <v>46.76555189179681</v>
+        <v>75.11842559044469</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.67180283380785</v>
+        <v>18.13582534055133</v>
       </c>
       <c r="C4" t="n">
-        <v>57.63644422092175</v>
+        <v>37.56068541677872</v>
       </c>
       <c r="D4" t="n">
-        <v>39.75587328347459</v>
+        <v>64.36239774271664</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.64940256305943</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C5" t="n">
-        <v>58.21763886183587</v>
+        <v>52.79348279587224</v>
       </c>
       <c r="D5" t="n">
-        <v>34.77841242294326</v>
+        <v>36.42283982755667</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.36984114706057</v>
+        <v>7.406304680837938</v>
       </c>
       <c r="C6" t="n">
-        <v>36.4277485660779</v>
+        <v>27.4113776502752</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>34.13340418125311</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>20.90042687571034</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.46010518258904</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04529479093201</v>
+        <v>16.07138149981443</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7240660170326</v>
+        <v>101.5034621040911</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015098263644004</v>
+        <v>3.383448736803037</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.108434215823654</v>
+        <v>3.392920065876976</v>
       </c>
       <c r="C2" t="n">
-        <v>9.559277396251192</v>
+        <v>7.395505456091222</v>
       </c>
       <c r="D2" t="n">
-        <v>29.14318060056657</v>
+        <v>28.31360379047801</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.14622365467055</v>
+        <v>6.916412576418779</v>
       </c>
       <c r="C3" t="n">
-        <v>33.76721228756904</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="D3" t="n">
-        <v>51.60065933521236</v>
+        <v>79.41357179652449</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.12528815771187</v>
+        <v>16.15760371649401</v>
       </c>
       <c r="C4" t="n">
-        <v>51.31889774409352</v>
+        <v>43.35496036724339</v>
       </c>
       <c r="D4" t="n">
-        <v>46.66050488744241</v>
+        <v>86.2887509693649</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.5808190924824</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="C5" t="n">
-        <v>62.46369768270332</v>
+        <v>61.26105674500098</v>
       </c>
       <c r="D5" t="n">
-        <v>32.86400439966199</v>
+        <v>50.04458922398117</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.34217228489241</v>
+        <v>15.21512592041707</v>
       </c>
       <c r="C6" t="n">
-        <v>44.1560664939088</v>
+        <v>57.19760299712343</v>
       </c>
       <c r="D6" t="n">
-        <v>31.71830482880595</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.347980655659875</v>
+        <v>7.785259294677205</v>
       </c>
       <c r="C7" t="n">
-        <v>23.35577788403162</v>
+        <v>29.16477905005999</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.37874329632356</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049578075989958</v>
+        <v>17.33833619029097</v>
       </c>
       <c r="C21" t="n">
-        <v>66.9709917219046</v>
+        <v>114.4330188559204</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405986297493723</v>
+        <v>4.334584047572743</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.028511741152163</v>
+        <v>2.024363766156923</v>
       </c>
       <c r="C2" t="n">
-        <v>9.957866964175397</v>
+        <v>6.863398200389452</v>
       </c>
       <c r="D2" t="n">
-        <v>25.5156228333746</v>
+        <v>29.86083817237098</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.71349390127595</v>
+        <v>9.267698328089891</v>
       </c>
       <c r="C3" t="n">
-        <v>36.0252320073367</v>
+        <v>24.60259746842507</v>
       </c>
       <c r="D3" t="n">
-        <v>63.61234249667208</v>
+        <v>82.89877614660067</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.87302005544944</v>
+        <v>14.58778913740336</v>
       </c>
       <c r="C4" t="n">
-        <v>71.95621623506572</v>
+        <v>46.55840312620073</v>
       </c>
       <c r="D4" t="n">
-        <v>62.88192220471245</v>
+        <v>104.4245763099162</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.91938318172731</v>
+        <v>23.4392264388926</v>
       </c>
       <c r="C5" t="n">
-        <v>81.41142837466676</v>
+        <v>70.21950454625312</v>
       </c>
       <c r="D5" t="n">
-        <v>42.46058820867456</v>
+        <v>66.95519342963247</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.73339089726815</v>
+        <v>22.13841073076558</v>
       </c>
       <c r="C6" t="n">
-        <v>76.5989011284489</v>
+        <v>77.36368259005717</v>
       </c>
       <c r="D6" t="n">
-        <v>35.50196048097316</v>
+        <v>44.71958967614647</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.77392029058275</v>
+        <v>12.81573453123786</v>
       </c>
       <c r="C7" t="n">
-        <v>46.95110220789945</v>
+        <v>55.45500082208532</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>26.03594911662541</v>
+        <v>31.96079651175491</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26784429893288</v>
+        <v>18.62666346339743</v>
       </c>
       <c r="C21" t="n">
-        <v>76.31236513879524</v>
+        <v>127.7256923204395</v>
       </c>
       <c r="D21" t="n">
-        <v>5.45088322419966</v>
+        <v>5.32190384668498</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.860632883725958</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C2" t="n">
-        <v>11.69556040069225</v>
+        <v>4.227405614486766</v>
       </c>
       <c r="D2" t="n">
-        <v>22.61063137650829</v>
+        <v>23.49027731951343</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.38813450054276</v>
+        <v>11.1722888743287</v>
       </c>
       <c r="C3" t="n">
-        <v>37.62548076525901</v>
+        <v>35.77488634275377</v>
       </c>
       <c r="D3" t="n">
-        <v>69.26230053461248</v>
+        <v>92.75552309723865</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.16129402759952</v>
+        <v>11.25671917689393</v>
       </c>
       <c r="C4" t="n">
-        <v>82.5365112437336</v>
+        <v>64.54107582488956</v>
       </c>
       <c r="D4" t="n">
-        <v>80.64762866076273</v>
+        <v>94.22716290590462</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.49709280018094</v>
+        <v>12.4681958439345</v>
       </c>
       <c r="C5" t="n">
-        <v>110.3238982647353</v>
+        <v>46.2157731774186</v>
       </c>
       <c r="D5" t="n">
-        <v>55.4687452899448</v>
+        <v>46.6330159517235</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.71580155404972</v>
+        <v>7.929576207201488</v>
       </c>
       <c r="C6" t="n">
-        <v>105.2178284549477</v>
+        <v>36.50825187782615</v>
       </c>
       <c r="D6" t="n">
-        <v>40.53341746523807</v>
+        <v>25.84156307118455</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.77498415374501</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>80.6073770048886</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>45.64635950895544</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.6218725696115</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.83959354690535</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.472035355207384</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.99440216548399</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.538030935806462</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
